--- a/data/trans_orig/P1802_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1802_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45324</t>
+          <t>44237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71930</t>
+          <t>71576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82794</t>
+          <t>84501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121012</t>
+          <t>120107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362313</t>
+          <t>362910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387636</t>
+          <t>386932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323825</t>
+          <t>324179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350431</t>
+          <t>351518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694206</t>
+          <t>695111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>732424</t>
+          <t>730717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>52997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84416</t>
+          <t>84734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>70395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104437</t>
+          <t>103324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130461</t>
+          <t>131404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176473</t>
+          <t>176740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>506080</t>
+          <t>505762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>540497</t>
+          <t>537499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459107</t>
+          <t>460220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493483</t>
+          <t>493149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977567</t>
+          <t>977300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023579</t>
+          <t>1022636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111459</t>
+          <t>109972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85390</t>
+          <t>86259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168667</t>
+          <t>167441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218783</t>
+          <t>217850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557638</t>
+          <t>559125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>594517</t>
+          <t>594343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537093</t>
+          <t>539280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575996</t>
+          <t>575127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1111700</t>
+          <t>1112633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1161816</t>
+          <t>1163042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128949</t>
+          <t>130330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>87501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124375</t>
+          <t>125259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184693</t>
+          <t>185125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240237</t>
+          <t>243694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517099</t>
+          <t>515718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557516</t>
+          <t>555807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524702</t>
+          <t>523818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562700</t>
+          <t>561576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1054888</t>
+          <t>1051431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1110432</t>
+          <t>1110000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60488</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93054</t>
+          <t>93744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110466</t>
+          <t>109956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152425</t>
+          <t>149553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178193</t>
+          <t>177661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230898</t>
+          <t>229806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384864</t>
+          <t>384174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417430</t>
+          <t>418623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344424</t>
+          <t>347296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>386383</t>
+          <t>386893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743869</t>
+          <t>744961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>796574</t>
+          <t>797106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70044</t>
+          <t>70414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77853</t>
+          <t>76583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>112268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128059</t>
+          <t>127762</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171893</t>
+          <t>172200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264286</t>
+          <t>263916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290308</t>
+          <t>291593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264411</t>
+          <t>265494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>299909</t>
+          <t>301179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>540199</t>
+          <t>539892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584033</t>
+          <t>584330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>59188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78247</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116780</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121577</t>
+          <t>122144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166839</t>
+          <t>166222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198391</t>
+          <t>197810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220539</t>
+          <t>219722</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283389</t>
+          <t>284507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321922</t>
+          <t>322246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>490328</t>
+          <t>490945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>535590</t>
+          <t>535023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>450601</t>
+          <t>447787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>532950</t>
+          <t>530340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>623660</t>
+          <t>621069</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>717621</t>
+          <t>719257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1094059</t>
+          <t>1093456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1227221</t>
+          <t>1223456</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2861400</t>
+          <t>2864010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2943749</t>
+          <t>2946563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2826921</t>
+          <t>2825285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2920882</t>
+          <t>2923473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5711671</t>
+          <t>5715436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5844833</t>
+          <t>5845436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54674</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51370</t>
+          <t>66257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>106337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>369402</t>
+          <t>376116</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345313</t>
+          <t>353479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384081</t>
+          <t>390158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278213</t>
+          <t>316883</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261830</t>
+          <t>296255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291331</t>
+          <t>332253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>647615</t>
+          <t>692998</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>621578</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>669585</t>
+          <t>715046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>63156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>70587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95476</t>
+          <t>101192</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>82072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122664</t>
+          <t>126080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>380103</t>
+          <t>431897</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363200</t>
+          <t>413734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394030</t>
+          <t>447225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>459472</t>
+          <t>444884</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441300</t>
+          <t>430496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479735</t>
+          <t>458149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>839575</t>
+          <t>876781</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812387</t>
+          <t>851893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>862888</t>
+          <t>895901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>82727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116797</t>
+          <t>120913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82707</t>
+          <t>93071</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>79551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98059</t>
+          <t>109157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>192297</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159698</t>
+          <t>168890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205522</t>
+          <t>217520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>439144</t>
+          <t>521611</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419541</t>
+          <t>499924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455995</t>
+          <t>538110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>459761</t>
+          <t>529068</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444409</t>
+          <t>512982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>471975</t>
+          <t>542588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>898905</t>
+          <t>1050679</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873284</t>
+          <t>1025456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>919108</t>
+          <t>1074086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>352966</t>
+          <t>112993</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>94709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>664994</t>
+          <t>136207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>144950</t>
+          <t>159163</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122362</t>
+          <t>141652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164192</t>
+          <t>175419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>497916</t>
+          <t>272156</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>283550</t>
+          <t>245849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>938768</t>
+          <t>297906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>534820</t>
+          <t>587624</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>222792</t>
+          <t>564410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>747590</t>
+          <t>605908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>567183</t>
+          <t>577000</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547941</t>
+          <t>560744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589771</t>
+          <t>594511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1102004</t>
+          <t>1164624</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661152</t>
+          <t>1138874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1316370</t>
+          <t>1190931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712133</t>
+          <t>736163</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712133</t>
+          <t>736163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712133</t>
+          <t>736163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599920</t>
+          <t>1436780</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599920</t>
+          <t>1436780</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599920</t>
+          <t>1436780</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>117386</t>
+          <t>122653</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98760</t>
+          <t>103616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135831</t>
+          <t>142238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140879</t>
+          <t>156470</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>139770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157463</t>
+          <t>172789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>258265</t>
+          <t>279123</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234619</t>
+          <t>256646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281203</t>
+          <t>306322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>443848</t>
+          <t>486693</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425403</t>
+          <t>467108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462474</t>
+          <t>505730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>405689</t>
+          <t>451017</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>389105</t>
+          <t>434698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418288</t>
+          <t>467717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>849537</t>
+          <t>937711</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826599</t>
+          <t>910512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>873183</t>
+          <t>960188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546568</t>
+          <t>607487</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546568</t>
+          <t>607487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546568</t>
+          <t>607487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107802</t>
+          <t>1216834</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107802</t>
+          <t>1216834</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107802</t>
+          <t>1216834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69396</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57487</t>
+          <t>61901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81316</t>
+          <t>86681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>85764</t>
+          <t>93851</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>81755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>136207</t>
+          <t>107047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>155161</t>
+          <t>168208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>151069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>186773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>298022</t>
+          <t>331847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286102</t>
+          <t>319524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309931</t>
+          <t>344304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>522053</t>
+          <t>344682</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471610</t>
+          <t>331486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>573202</t>
+          <t>356778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>820075</t>
+          <t>676530</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>772633</t>
+          <t>657965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>897740</t>
+          <t>693669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>406205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607817</t>
+          <t>438533</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607817</t>
+          <t>438533</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607817</t>
+          <t>438533</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975236</t>
+          <t>844738</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975236</t>
+          <t>844738</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975236</t>
+          <t>844738</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>59698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87450</t>
+          <t>95349</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76678</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99025</t>
+          <t>108025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>132890</t>
+          <t>143483</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118123</t>
+          <t>126835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148980</t>
+          <t>160660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>236607</t>
+          <t>261268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226767</t>
+          <t>249704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246481</t>
+          <t>270654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>337815</t>
+          <t>368664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326240</t>
+          <t>355988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348587</t>
+          <t>382055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>574422</t>
+          <t>629932</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>558332</t>
+          <t>612755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>589189</t>
+          <t>646580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>309402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>309402</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>309402</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707312</t>
+          <t>773415</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707312</t>
+          <t>773415</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707312</t>
+          <t>773415</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>535648</t>
+          <t>492282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1357470</t>
+          <t>581716</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>519238</t>
+          <t>660448</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>689500</t>
+          <t>745858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1146383</t>
+          <t>1170974</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2120306</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2701945</t>
+          <t>2997057</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2100887</t>
+          <t>2949375</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2922709</t>
+          <t>3038809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3030187</t>
+          <t>3032198</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2969456</t>
+          <t>2986073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3139718</t>
+          <t>3071483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5732132</t>
+          <t>6029256</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4997007</t>
+          <t>5972558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5970930</t>
+          <t>6092048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
